--- a/02_DIA_inicio_2026_analisis_assets/rbd_9431_escuela-villa-san-miguel_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9431_escuela-villa-san-miguel_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2D1A775-8AB8-4A43-BBEB-C2F0376879B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39F50F01-025D-45F9-9BBF-628326E598ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E720D8C-0469-46D0-8D1D-99D66C7920F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5807A01-5A40-40C9-B2A7-1B3126EE8A20}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C563A976-736E-40BC-A6D2-78A2850128CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCC60C19-95C3-4B3C-A882-A2F8EC847F02}"/>
 </file>